--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -684,7 +684,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +932,11 @@
           <t>76.286.397-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>96.799.250-k</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1440,11 @@
           <t>77.015.597-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1688,11 @@
           <t>76.376.088-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1753,11 @@
           <t>96.771.610-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2062,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2249,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2436,11 @@
           <t>76.734.221-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2501,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2566,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2631,11 @@
           <t>76.504.980-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2696,11 @@
           <t>76.811.563-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2761,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2826,11 @@
           <t>77.185.932-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2891,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3139,11 @@
           <t>76.891.821-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3265,11 @@
           <t>76.384.526-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3391,11 @@
           <t>77.146.212-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3578,11 @@
           <t>77.479.175-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3643,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3830,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3895,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3960,11 @@
           <t>77.347.464-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4147,11 @@
           <t>77.077.350-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4212,11 @@
           <t>96.777.670-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4399,11 @@
           <t>76.304.354-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4479,7 +4599,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1219102-81-CM25</t>
+          <t>1057547-28151-SE25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,43 +4624,47 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>62.000.930-k</t>
+          <t>61.607.502-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Defensoría del Contribuyente</t>
+          <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Andes Digital</t>
+          <t>DJC SERVICIOS INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>77.160.932-5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>19296.11</v>
+        <v>45677.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1076403-26-CM25</t>
+          <t>1219102-81-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4560,17 +4684,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>62.000.930-k</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>Defensoría del Contribuyente</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4704,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TCHILECOM</t>
+          <t>Andes Digital</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.349.120-8</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,6 +4719,67 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
+        <v>19296.11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1076403-26-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.601.000-1</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TCHILECOM</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.349.120-8</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>51573.62</v>
       </c>
     </row>

--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/ago-2025.xlsx
@@ -749,7 +749,11 @@
           <t>76.164.712-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4338,7 +4342,11 @@
           <t>96.616.770-k</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
